--- a/xls/square_un_16_tri3_16_0.xlsx
+++ b/xls/square_un_16_tri3_16_0.xlsx
@@ -482,13 +482,13 @@
         <v>1842</v>
       </c>
       <c r="I16">
-        <v>-3.3008323673689404</v>
+        <v>-2.290716268075585</v>
       </c>
       <c r="J16">
-        <v>-2.67355274645929</v>
+        <v>-1.971473986251402</v>
       </c>
       <c r="K16">
-        <v>-9.350995522204748</v>
+        <v>-0.7821369248958212</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_un_16_tri3_16_0.xlsx
+++ b/xls/square_un_16_tri3_16_0.xlsx
@@ -461,34 +461,34 @@
         <v>11</v>
       </c>
       <c r="B16">
-        <v>340</v>
+        <v>297</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
       </c>
       <c r="D16">
-        <v>340</v>
+        <v>297</v>
       </c>
       <c r="E16" t="s">
         <v>12</v>
       </c>
       <c r="F16">
-        <v>340</v>
+        <v>297</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
       </c>
       <c r="H16">
-        <v>1842</v>
+        <v>1596</v>
       </c>
       <c r="I16">
-        <v>-2.290716268075585</v>
+        <v>-2.224577373896808</v>
       </c>
       <c r="J16">
-        <v>-1.971473986251402</v>
+        <v>-1.9742906504243845</v>
       </c>
       <c r="K16">
-        <v>-0.7821369248958212</v>
+        <v>-0.8632754337090655</v>
       </c>
     </row>
   </sheetData>
